--- a/all_sim/gemini_pet.xlsx
+++ b/all_sim/gemini_pet.xlsx
@@ -331,13 +331,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="26.400000000000002" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.5757722007722008</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.02380952380952382</v>
+        <v>0.4976190476190476</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.6481481481481481</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.25925925925925924</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.25925925925925924</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.25925925925925924</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.22222222222222224</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.22222222222222224</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.46551724137931033</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.46551724137931033</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -482,13 +482,13 @@
         <v>1.0</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.15476190476190477</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.530982905982906</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.530982905982906</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.530982905982906</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.530982905982906</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.46296296296296297</v>
       </c>
     </row>
     <row r="6">
@@ -538,31 +538,31 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.7833333333333333</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.2253968253968254</v>
+        <v>0.6126984126984127</v>
       </c>
     </row>
     <row r="7">
@@ -578,28 +578,28 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.9666666666666666</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.13333333333333336</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.1</v>
+        <v>0.522972972972973</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.06666666666666668</v>
+        <v>0.5063063063063064</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.1</v>
+        <v>0.522972972972973</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.06666666666666668</v>
+        <v>0.5063063063063064</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5563063063063063</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.09166666666666667</v>
+        <v>0.5201923076923076</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.32575757575757575</v>
+        <v>0.6628787878787878</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.32575757575757575</v>
+        <v>0.6628787878787878</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.32575757575757575</v>
+        <v>0.6628787878787878</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.29545454545454547</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.29545454545454547</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.29545454545454547</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.29545454545454547</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.29797979797979796</v>
+        <v>0.648989898989899</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.29797979797979796</v>
+        <v>0.648989898989899</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.29797979797979796</v>
+        <v>0.648989898989899</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.5707070707070707</v>
+        <v>0.7853535353535354</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.5737373737373738</v>
+        <v>0.7868686868686869</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.5737373737373738</v>
+        <v>0.7868686868686869</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.5737373737373738</v>
+        <v>0.7868686868686869</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.5737373737373738</v>
+        <v>0.7868686868686869</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
     </row>
     <row r="10">
@@ -695,22 +695,22 @@
         <v>1.0</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="11">
@@ -723,31 +723,31 @@
         <v>1.0</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5651948561568778</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5659060937102207</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5655552165172382</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5659060937102207</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5659060937102207</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5662478572098789</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5662478572098789</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5655552165172382</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.1844437663678098</v>
+        <v>0.5655552165172382</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.14180779531272109</v>
+        <v>0.5445881081826763</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.3782051282051282</v>
+        <v>0.6891025641025641</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.37606837606837606</v>
+        <v>0.688034188034188</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.37606837606837606</v>
+        <v>0.688034188034188</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.37606837606837606</v>
+        <v>0.688034188034188</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.37606837606837606</v>
+        <v>0.688034188034188</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.09246309246309246</v>
+        <v>0.44819233054527174</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.0038220777657397374</v>
+        <v>0.2547519479737789</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.6447802197802198</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.6447802197802198</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.6447802197802198</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.37202380952380953</v>
+        <v>0.6698828725038403</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.5464285714285715</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.14484126984126985</v>
+        <v>0.5079045058883769</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.14484126984126985</v>
+        <v>0.5079045058883769</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.25793650793650796</v>
+        <v>0.5600027367268746</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.25793650793650796</v>
+        <v>0.5600027367268746</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.25793650793650796</v>
+        <v>0.5600027367268746</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.25793650793650796</v>
+        <v>0.5600027367268746</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.25793650793650796</v>
+        <v>0.5600027367268746</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.2341269841269841</v>
+        <v>0.5503968253968254</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.6148570708079385</v>
+        <v>0.8074285354039692</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.6193067022956136</v>
+        <v>0.8096533511478068</v>
       </c>
     </row>
     <row r="21">
@@ -1093,31 +1093,31 @@
         <v>1.0</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -1127,34 +1127,34 @@
         </is>
       </c>
       <c r="B22" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="23">
@@ -1164,34 +1164,34 @@
         </is>
       </c>
       <c r="B23" s="0" t="n">
-        <v>0.3956876456876457</v>
+        <v>0.6978438228438228</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>0.46468864468864474</v>
+        <v>0.6414352314352314</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.25155677655677655</v>
+        <v>0.5852378477378477</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>0.1677045177045177</v>
+        <v>0.5338522588522588</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>0.1944139194139194</v>
+        <v>0.5537286988373945</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>0.2698168498168497</v>
+        <v>0.5479519031692944</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>0.1944139194139194</v>
+        <v>0.5416514041514041</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>0.1686355311355311</v>
+        <v>0.5128891941391942</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>0.15178155178155175</v>
+        <v>0.4572467080941657</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>0.08332025117739403</v>
+        <v>0.39582679225536366</v>
       </c>
     </row>
     <row r="24">
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="B24" s="0" t="n">
-        <v>0.31333333333333335</v>
+        <v>0.6078861788617886</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>0.5822222222222223</v>
+        <v>0.7772222222222223</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.22083333333333333</v>
+        <v>0.5719551282051283</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>0.18958333333333333</v>
+        <v>0.5407376126126127</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>0.18958333333333333</v>
+        <v>0.5407376126126127</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
       <c r="K24" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
     </row>
     <row r="25">
@@ -1238,34 +1238,34 @@
         </is>
       </c>
       <c r="B25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K25" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -1287,22 +1287,22 @@
         <v>1.0</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="27">
@@ -1312,34 +1312,34 @@
         </is>
       </c>
       <c r="B27" s="0" t="n">
-        <v>0.5717171717171717</v>
+        <v>0.7546085858585858</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>0.5668537224092778</v>
+        <v>0.7516808294586071</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.5565656565656566</v>
+        <v>0.7470328282828282</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>0.07654320987654321</v>
+        <v>0.4737554759060135</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>0.07654320987654321</v>
+        <v>0.4737554759060135</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
     </row>
     <row r="28">
@@ -1349,34 +1349,34 @@
         </is>
       </c>
       <c r="B28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="K28" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -1389,31 +1389,31 @@
         <v>1.0</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K29" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30">
@@ -1423,34 +1423,34 @@
         </is>
       </c>
       <c r="B30" s="0" t="n">
-        <v>0.27936507936507937</v>
+        <v>0.6396825396825396</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>0.3705853174603175</v>
+        <v>0.6852926587301588</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.353125</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
       <c r="F30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
       <c r="K30" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
     </row>
     <row r="31">
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="B31" s="0" t="n">
-        <v>0.39285714285714285</v>
+        <v>0.6339285714285714</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>0.27142857142857146</v>
+        <v>0.5711981566820277</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.48541666666666666</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.483117816091954</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
       <c r="K31" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
     </row>
     <row r="32">
@@ -1497,34 +1497,34 @@
         </is>
       </c>
       <c r="B32" s="0" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="K32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="33">
@@ -1537,31 +1537,31 @@
         <v>1.0</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K33" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="34">
@@ -1576,31 +1576,31 @@
         </is>
       </c>
       <c r="C34" s="0" t="n">
-        <v>0.2017609126984127</v>
+        <v>0.4365947420634921</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.2690145502645503</v>
+        <v>0.5528746220710506</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>0.2690145502645503</v>
+        <v>0.5266641378773732</v>
       </c>
       <c r="F34" s="0" t="n">
-        <v>0.1511904761904762</v>
+        <v>0.4818452380952381</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.4506324404761905</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.46829548395445136</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.46829548395445136</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.46829548395445136</v>
       </c>
       <c r="K34" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.46829548395445136</v>
       </c>
     </row>
     <row r="35">

--- a/all_sim/gemini_pet.xlsx
+++ b/all_sim/gemini_pet.xlsx
@@ -331,13 +331,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="26.400000000000002" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.5757722007722008</v>
+        <v>0.1737451737451738</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.4976190476190476</v>
+        <v>0.02312925170068028</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.6481481481481481</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.22222222222222224</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.22222222222222224</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.46551724137931033</v>
+        <v>0.0</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.46551724137931033</v>
+        <v>0.0</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -482,13 +482,13 @@
         <v>1.0</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.1437074829931973</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.0</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.0</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.0</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.530982905982906</v>
+        <v>0.12820512820512822</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.530982905982906</v>
+        <v>0.12820512820512822</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.530982905982906</v>
+        <v>0.12820512820512822</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.530982905982906</v>
+        <v>0.12820512820512822</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.46296296296296297</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -538,31 +538,31 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9583333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.8916666666666666</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.6126984126984127</v>
+        <v>0.2253968253968254</v>
       </c>
     </row>
     <row r="7">
@@ -578,28 +578,28 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9666666666666666</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.13333333333333336</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.522972972972973</v>
+        <v>0.0945945945945946</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.5063063063063064</v>
+        <v>0.06306306306306307</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.522972972972973</v>
+        <v>0.0945945945945946</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.5063063063063064</v>
+        <v>0.06306306306306307</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.5563063063063063</v>
+        <v>0.15765765765765768</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.5201923076923076</v>
+        <v>0.08696581196581198</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.6628787878787878</v>
+        <v>0.32575757575757575</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.6628787878787878</v>
+        <v>0.32575757575757575</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.6628787878787878</v>
+        <v>0.32575757575757575</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.29545454545454547</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.29545454545454547</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.29545454545454547</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.29545454545454547</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.648989898989899</v>
+        <v>0.29797979797979796</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.648989898989899</v>
+        <v>0.29797979797979796</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.648989898989899</v>
+        <v>0.29797979797979796</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.7853535353535354</v>
+        <v>0.5707070707070707</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.7868686868686869</v>
+        <v>0.5737373737373738</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.7868686868686869</v>
+        <v>0.5737373737373738</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.7868686868686869</v>
+        <v>0.5737373737373738</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.7868686868686869</v>
+        <v>0.5737373737373738</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
     </row>
     <row r="10">
@@ -695,22 +695,22 @@
         <v>1.0</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="11">
@@ -723,31 +723,31 @@
         <v>1.0</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.5651948561568778</v>
+        <v>0.17447383305063088</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.5659060937102207</v>
+        <v>0.17473619971687243</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5655552165172382</v>
+        <v>0.17460676549485993</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.5659060937102207</v>
+        <v>0.17473619971687243</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5659060937102207</v>
+        <v>0.17473619971687243</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.5662478572098789</v>
+        <v>0.17486227201104046</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.5662478572098789</v>
+        <v>0.17486227201104046</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.5655552165172382</v>
+        <v>0.17460676549485993</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.5655552165172382</v>
+        <v>0.17460676549485993</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.5445881081826763</v>
+        <v>0.13434422713836736</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.6891025641025641</v>
+        <v>0.3782051282051282</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.688034188034188</v>
+        <v>0.37606837606837606</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.688034188034188</v>
+        <v>0.37606837606837606</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.688034188034188</v>
+        <v>0.37606837606837606</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.688034188034188</v>
+        <v>0.37606837606837606</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.44819233054527174</v>
+        <v>0.07433307433307433</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.2547519479737789</v>
+        <v>0.0019327552338115714</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.6447802197802198</v>
+        <v>0.35769230769230775</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.6447802197802198</v>
+        <v>0.35769230769230775</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.6447802197802198</v>
+        <v>0.35769230769230775</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.6698828725038403</v>
+        <v>0.3600230414746544</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.5464285714285715</v>
+        <v>0.19603174603174603</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.5079045058883769</v>
+        <v>0.12615207373271892</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.5079045058883769</v>
+        <v>0.12615207373271892</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.5600027367268746</v>
+        <v>0.22235905856595511</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.5600027367268746</v>
+        <v>0.22235905856595511</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.5600027367268746</v>
+        <v>0.22235905856595511</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.5600027367268746</v>
+        <v>0.22235905856595511</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.5600027367268746</v>
+        <v>0.22235905856595511</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.5503968253968254</v>
+        <v>0.2029100529100529</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.8074285354039692</v>
+        <v>0.6148570708079385</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.8096533511478068</v>
+        <v>0.6193067022956136</v>
       </c>
     </row>
     <row r="21">
@@ -1093,31 +1093,31 @@
         <v>1.0</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K21" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="22">
@@ -1127,34 +1127,34 @@
         </is>
       </c>
       <c r="B22" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="H22" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="K22" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
     </row>
     <row r="23">
@@ -1164,34 +1164,34 @@
         </is>
       </c>
       <c r="B23" s="0" t="n">
-        <v>0.6978438228438228</v>
+        <v>0.3956876456876457</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>0.6414352314352314</v>
+        <v>0.3801998001998002</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.5852378477378477</v>
+        <v>0.23116028116028114</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>0.5338522588522588</v>
+        <v>0.15093406593406591</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>0.5537286988373945</v>
+        <v>0.17750836120401337</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>0.5479519031692944</v>
+        <v>0.22289218028348456</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>0.5416514041514041</v>
+        <v>0.17281237281237277</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>0.5128891941391942</v>
+        <v>0.14454474097331238</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>0.4572467080941657</v>
+        <v>0.1157655903418615</v>
       </c>
       <c r="K23" s="0" t="n">
-        <v>0.39582679225536366</v>
+        <v>0.0590185112506541</v>
       </c>
     </row>
     <row r="24">
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="B24" s="0" t="n">
-        <v>0.6078861788617886</v>
+        <v>0.28276422764227643</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>0.7772222222222223</v>
+        <v>0.5660493827160494</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.5719551282051283</v>
+        <v>0.20384615384615384</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>0.5407376126126127</v>
+        <v>0.16908783783783782</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>0.5407376126126127</v>
+        <v>0.16908783783783782</v>
       </c>
       <c r="G24" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
       <c r="H24" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
       <c r="K24" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
     </row>
     <row r="25">
@@ -1238,34 +1238,34 @@
         </is>
       </c>
       <c r="B25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K25" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26">
@@ -1287,22 +1287,22 @@
         <v>1.0</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G26" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="27">
@@ -1312,34 +1312,34 @@
         </is>
       </c>
       <c r="B27" s="0" t="n">
-        <v>0.7546085858585858</v>
+        <v>0.5359848484848485</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>0.7516808294586071</v>
+        <v>0.5308630098753554</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.7470328282828282</v>
+        <v>0.5217803030303031</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>0.4737554759060135</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>0.4737554759060135</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
       <c r="H27" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
     </row>
     <row r="28">
@@ -1349,34 +1349,34 @@
         </is>
       </c>
       <c r="B28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K28" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="29">
@@ -1389,31 +1389,31 @@
         <v>1.0</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K29" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30">
@@ -1423,34 +1423,34 @@
         </is>
       </c>
       <c r="B30" s="0" t="n">
-        <v>0.6396825396825396</v>
+        <v>0.27936507936507937</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>0.6852926587301588</v>
+        <v>0.3705853174603175</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.353125</v>
+        <v>0.012890625</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
       <c r="F30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
       <c r="G30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
       <c r="H30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
       <c r="I30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
       <c r="J30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
       <c r="K30" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
     </row>
     <row r="31">
@@ -1460,34 +1460,34 @@
         </is>
       </c>
       <c r="B31" s="0" t="n">
-        <v>0.6339285714285714</v>
+        <v>0.34375</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>0.5711981566820277</v>
+        <v>0.2364055299539171</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.48541666666666666</v>
+        <v>0.09027777777777778</v>
       </c>
       <c r="E31" s="0" t="n">
-        <v>0.483117816091954</v>
+        <v>0.08979885057471262</v>
       </c>
       <c r="F31" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="G31" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="H31" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="I31" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="K31" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -1497,34 +1497,34 @@
         </is>
       </c>
       <c r="B32" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="G32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="I32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="K32" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="33">
@@ -1537,31 +1537,31 @@
         <v>1.0</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K33" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -1576,31 +1576,31 @@
         </is>
       </c>
       <c r="C34" s="0" t="n">
-        <v>0.4365947420634921</v>
+        <v>0.13546804138321997</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.5528746220710506</v>
+        <v>0.22509380736421555</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>0.5266641378773732</v>
+        <v>0.21099180412905905</v>
       </c>
       <c r="F34" s="0" t="n">
-        <v>0.4818452380952381</v>
+        <v>0.12284226190476191</v>
       </c>
       <c r="G34" s="0" t="n">
-        <v>0.4506324404761905</v>
+        <v>0.07212146577380953</v>
       </c>
       <c r="H34" s="0" t="n">
-        <v>0.46829548395445136</v>
+        <v>0.07525718167701864</v>
       </c>
       <c r="I34" s="0" t="n">
-        <v>0.46829548395445136</v>
+        <v>0.07525718167701864</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>0.46829548395445136</v>
+        <v>0.07525718167701864</v>
       </c>
       <c r="K34" s="0" t="n">
-        <v>0.46829548395445136</v>
+        <v>0.07525718167701864</v>
       </c>
     </row>
     <row r="35">
